--- a/output/billing_report/00_audit_extraktion.xlsx
+++ b/output/billing_report/00_audit_extraktion.xlsx
@@ -18,6 +18,8 @@
     <sheet name="EBM-Papst Mulfingen" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Fischerwerke GmbH &amp; Co KG" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Groz-Beckert KG" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Sika Automotive AG" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sika Automotive DE" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -516,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1854,6 +1856,226 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sika Automotive AG</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>527406</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>420</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="V13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z13" s="5" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AA13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH13" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Sika Automotive DE</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>413276+493163</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>448</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>
@@ -3428,6 +3650,1572 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Daten-Qualität: Sika Automotive AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>N Zeilen</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Gefüllt%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Fehlt%</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>✗ Lückenhaft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Fracht</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Diesel</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Maut/SSD</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Gesamt</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>AX Fracht</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>AX Diesel</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>AX Maut</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>AX Nebengebühr</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>AX Gesamt</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Daten-Qualität: Sika Automotive DE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>N Zeilen</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Gefüllt%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Fehlt%</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>✗ Lückenhaft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Fracht</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Diesel</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Maut/SSD</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Gesamt</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>448</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>AX Fracht</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>AX Diesel</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>AX Maut</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>AX Nebengebühr</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>AX Gesamt</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>481</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/billing_report/00_audit_extraktion.xlsx
+++ b/output/billing_report/00_audit_extraktion.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>DINAS fehlgeschlagen (ca.)</t>
+          <t>DINAS 0-Pos/Cover PDFs</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>0</v>
+        <v>333</v>
       </c>
       <c r="E6" s="8" t="n">
         <v>442</v>
@@ -1096,7 +1096,7 @@
         <v>275</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>323</v>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>410912</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -1774,12 +1774,10 @@
         <v>1854</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+        <v>754</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>15</v>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -1819,41 +1817,41 @@
       <c r="V12" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="W12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="6" t="n">
-        <v>0</v>
+      <c r="W12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z12" s="5" t="n">
+        <v>98</v>
+      </c>
+      <c r="AA12" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="AB12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH12" s="5" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3287,17 +3285,17 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3318,17 +3316,17 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3349,17 +3347,17 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3380,17 +3378,17 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>98</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3411,17 +3409,17 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>99.90000000000001</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>100</v>
+        <v>0.1</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3442,17 +3440,17 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3473,17 +3471,17 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3504,17 +3502,17 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3535,17 +3533,17 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3566,17 +3564,17 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3595,17 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3628,17 +3626,17 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
+        <v>754</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>

--- a/output/billing_report/00_audit_extraktion.xlsx
+++ b/output/billing_report/00_audit_extraktion.xlsx
@@ -10,16 +10,17 @@
     <sheet name="Zusammenfassung" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="HELU KABEL GmbH" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sika Dtl. CH AG &amp; Co KG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="GEZE GmbH" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="HERMA GmbH" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Bitzer Kühlmaschinenbau" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="CHT Germany GmbH" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Konrad Hornschuch GmbH" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="EBM-Papst Mulfingen" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Fischerwerke GmbH &amp; Co KG" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Groz-Beckert KG" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sika Automotive AG" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Sika Automotive DE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Sika Supply Center GmbH" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GEZE GmbH" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="HERMA GmbH" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Bitzer Kühlmaschinenbau" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="CHT Germany GmbH" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Konrad Hornschuch GmbH" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="EBM-Papst Mulfingen" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Fischerwerke GmbH &amp; Co KG" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Groz-Beckert KG" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Sika Automotive AG" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Sika Automotive DE" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,7 +519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -963,34 +964,34 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>GEZE GmbH</t>
+          <t>Sika Supply Center GmbH</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>406035</t>
+          <t>511241</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>543</v>
+        <v>1191</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>7752</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -1002,107 +1003,107 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="L5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>100</v>
+      <c r="L5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O5" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="R5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="S5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="U5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="V5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z5" s="5" t="n">
-        <v>99.3</v>
-      </c>
-      <c r="AA5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG5" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH5" s="5" t="n">
-        <v>100</v>
+      <c r="P5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>HERMA GmbH</t>
+          <t>GEZE GmbH</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>423650</t>
+          <t>406035</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>319</v>
+        <v>185</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>333</v>
+        <v>113</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>442</v>
+        <v>543</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>275</v>
+        <v>76</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>5112</v>
+        <v>7752</v>
       </c>
       <c r="J6" s="7" t="inlineStr">
         <is>
@@ -1114,23 +1115,23 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="L6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>0</v>
+      <c r="L6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O6" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v>0</v>
+      <c r="P6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="R6" s="5" t="n">
         <v>100</v>
@@ -1138,47 +1139,47 @@
       <c r="S6" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="T6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="6" t="n">
-        <v>0</v>
+      <c r="T6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="W6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" s="6" t="n">
-        <v>0</v>
+      <c r="W6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z6" s="5" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="AA6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="AD6" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="AE6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="6" t="n">
-        <v>0</v>
+      <c r="AE6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF6" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG6" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="AH6" s="5" t="n">
         <v>100</v>
@@ -1187,34 +1188,34 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bitzer Kühlmaschinenbau</t>
+          <t>HERMA GmbH</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>406345</t>
+          <t>423650</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4391</v>
+        <v>319</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2004</v>
+        <v>333</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4541</v>
+        <v>442</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4214</v>
+        <v>275</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>177</v>
+        <v>44</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1596</v>
+        <v>323</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>3474</v>
+        <v>5112</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -1226,23 +1227,23 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>100</v>
+      <c r="L7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="5" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>100</v>
+      <c r="P7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="5" t="n">
         <v>100</v>
@@ -1250,47 +1251,47 @@
       <c r="S7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="T7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="U7" s="5" t="n">
-        <v>100</v>
+      <c r="T7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="W7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z7" s="5" t="n">
-        <v>99</v>
-      </c>
-      <c r="AA7" s="5" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="AB7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC7" s="5" t="n">
-        <v>100</v>
+      <c r="W7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="AD7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="AE7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF7" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG7" s="5" t="n">
-        <v>100</v>
+      <c r="AE7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="AH7" s="5" t="n">
         <v>100</v>
@@ -1299,34 +1300,34 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>CHT Germany GmbH</t>
+          <t>Bitzer Kühlmaschinenbau</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>486073</t>
+          <t>406345</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>179</v>
+        <v>4391</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>191</v>
+        <v>2004</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>144</v>
+        <v>4541</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>90</v>
+        <v>4214</v>
       </c>
       <c r="G8" s="8" t="n">
-        <v>89</v>
+        <v>177</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="I8" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
@@ -1351,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>100</v>
@@ -1381,10 +1382,10 @@
         <v>100</v>
       </c>
       <c r="Z8" s="5" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="AA8" s="5" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AB8" s="5" t="n">
         <v>100</v>
@@ -1411,34 +1412,34 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Konrad Hornschuch GmbH</t>
+          <t>CHT Germany GmbH</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>490085</t>
+          <t>486073</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>263</v>
+        <v>179</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>155</v>
+        <v>191</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>382</v>
+        <v>144</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1463,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="Q9" s="5" t="n">
         <v>100</v>
@@ -1493,7 +1494,7 @@
         <v>100</v>
       </c>
       <c r="Z9" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AA9" s="5" t="n">
         <v>100</v>
@@ -1523,34 +1524,34 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>EBM-Papst Mulfingen</t>
+          <t>Konrad Hornschuch GmbH</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>410844</t>
+          <t>490085</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>162</v>
+        <v>263</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>178</v>
+        <v>155</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>123</v>
+        <v>382</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="G10" s="8" t="n">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
@@ -1574,8 +1575,8 @@
       <c r="O10" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P10" s="6" t="n">
-        <v>28.6</v>
+      <c r="P10" s="5" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>100</v>
@@ -1605,10 +1606,10 @@
         <v>100</v>
       </c>
       <c r="Z10" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AA10" s="5" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="AB10" s="5" t="n">
         <v>100</v>
@@ -1635,34 +1636,34 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Fischerwerke GmbH &amp; Co KG</t>
+          <t>EBM-Papst Mulfingen</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>409480</t>
+          <t>410844</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1500</v>
+        <v>162</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>383</v>
+        <v>178</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1347</v>
+        <v>123</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>718</v>
+        <v>118</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>782</v>
+        <v>44</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1686,8 +1687,8 @@
       <c r="O11" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P11" s="5" t="n">
-        <v>98.09999999999999</v>
+      <c r="P11" s="6" t="n">
+        <v>28.6</v>
       </c>
       <c r="Q11" s="5" t="n">
         <v>100</v>
@@ -1717,10 +1718,10 @@
         <v>100</v>
       </c>
       <c r="Z11" s="5" t="n">
-        <v>99.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AA11" s="5" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="AB11" s="5" t="n">
         <v>100</v>
@@ -1747,37 +1748,39 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>Groz-Beckert KG</t>
+          <t>Fischerwerke GmbH &amp; Co KG</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>410912</t>
+          <t>409480</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1312</v>
+        <v>1500</v>
       </c>
       <c r="D12" s="8" t="n">
-        <v>129</v>
+        <v>383</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1854</v>
+        <v>1347</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>1137</v>
+        <v>718</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>175</v>
+        <v>782</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>754</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <v>15</v>
+        <v>1883</v>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
@@ -1785,22 +1788,22 @@
         </is>
       </c>
       <c r="L12" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>98.90000000000001</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>76.7</v>
+        <v>100</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v>0</v>
+      <c r="P12" s="5" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="Q12" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>100</v>
@@ -1827,10 +1830,10 @@
         <v>100</v>
       </c>
       <c r="Z12" s="5" t="n">
-        <v>98</v>
+        <v>99.5</v>
       </c>
       <c r="AA12" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AB12" s="5" t="n">
         <v>100</v>
@@ -1857,37 +1860,37 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Sika Automotive AG</t>
+          <t>Groz-Beckert KG</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>527406</t>
+          <t>410912</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0</v>
+        <v>1312</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0</v>
+        <v>1854</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
@@ -1895,22 +1898,22 @@
         </is>
       </c>
       <c r="L13" s="5" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>76.7</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P13" s="5" t="n">
-        <v>96</v>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>100</v>
+      <c r="P13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="R13" s="5" t="n">
         <v>100</v>
@@ -1937,10 +1940,10 @@
         <v>100</v>
       </c>
       <c r="Z13" s="5" t="n">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="AA13" s="5" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AB13" s="5" t="n">
         <v>100</v>
@@ -1967,110 +1970,220 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
+          <t>Sika Automotive AG</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>527406</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>303</v>
+      </c>
+      <c r="I14" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="J14" s="8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="V14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z14" s="5" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AA14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
           <t>Sika Automotive DE</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>413276+493163</t>
         </is>
       </c>
-      <c r="C14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="8" t="n">
+      <c r="C15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="4" t="n">
         <v>448</v>
       </c>
-      <c r="I14" s="8" t="n">
+      <c r="I15" s="4" t="n">
         <v>481</v>
       </c>
-      <c r="J14" s="8" t="n">
+      <c r="J15" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="L14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="O14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="R14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="U14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="V14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="W14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="X14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z14" s="5" t="n">
+      <c r="L15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="O15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="R15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="S15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="V15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z15" s="5" t="n">
         <v>96.5</v>
       </c>
-      <c r="AA14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AC14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AD14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AG14" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AH14" s="5" t="n">
+      <c r="AA15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AC15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AD15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AE15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH15" s="5" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2103,7 +2216,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: Fischerwerke GmbH &amp; Co KG</t>
+          <t>Daten-Qualität: EBM-Papst Mulfingen</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2274,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>100</v>
@@ -2192,7 +2305,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>100</v>
@@ -2223,7 +2336,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>100</v>
@@ -2254,7 +2367,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -2285,17 +2398,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>526</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>98.09999999999999</v>
+        <v>49</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>28.6</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.9</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2429,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>100</v>
@@ -2347,7 +2460,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -2378,7 +2491,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -2409,7 +2522,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -2440,7 +2553,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -2471,7 +2584,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>526</v>
+        <v>49</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -2502,7 +2615,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -2533,7 +2646,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -2564,7 +2677,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -2595,13 +2708,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>99.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.5</v>
+        <v>2.4</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -2626,13 +2739,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -2657,7 +2770,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -2688,7 +2801,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -2719,7 +2832,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -2750,7 +2863,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -2781,7 +2894,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -2812,7 +2925,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -2843,7 +2956,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>1883</v>
+        <v>379</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -2886,7 +2999,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: Groz-Beckert KG</t>
+          <t>Daten-Qualität: Fischerwerke GmbH &amp; Co KG</t>
         </is>
       </c>
     </row>
@@ -2944,13 +3057,13 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -2975,13 +3088,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>98.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3006,17 +3119,17 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1854</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>76.7</v>
+        <v>526</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>⚠ Teilweise</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3150,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -3068,17 +3181,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1854</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>526</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>98.09999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>99</v>
+        <v>1.9</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3099,17 +3212,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1854</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>526</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3243,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -3161,7 +3274,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -3192,7 +3305,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -3223,7 +3336,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -3254,7 +3367,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1854</v>
+        <v>526</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -3285,7 +3398,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -3316,7 +3429,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -3347,7 +3460,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -3378,13 +3491,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>98</v>
+        <v>99.5</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -3409,13 +3522,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -3440,7 +3553,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -3471,7 +3584,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -3502,7 +3615,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -3533,7 +3646,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -3564,7 +3677,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -3595,7 +3708,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -3626,7 +3739,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>754</v>
+        <v>1883</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -3669,7 +3782,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: Sika Automotive AG</t>
+          <t>Daten-Qualität: Groz-Beckert KG</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3840,13 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
@@ -3758,13 +3871,13 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
@@ -3789,17 +3902,17 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>100</v>
+        <v>1854</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>76.7</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>⚠ Teilweise</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3933,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -3851,17 +3964,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>96</v>
+        <v>1854</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -3882,17 +3995,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>303</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>100</v>
+        <v>1854</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -3913,7 +4026,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -3944,7 +4057,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -3975,7 +4088,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -4006,7 +4119,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -4037,7 +4150,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>303</v>
+        <v>1854</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -4068,7 +4181,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -4099,7 +4212,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -4130,7 +4243,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -4161,13 +4274,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>98.3</v>
+        <v>98</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -4192,13 +4305,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -4223,7 +4336,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -4254,7 +4367,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -4285,7 +4398,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -4316,7 +4429,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -4347,7 +4460,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -4378,7 +4491,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -4409,7 +4522,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>420</v>
+        <v>754</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -4452,6 +4565,789 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
+          <t>Daten-Qualität: Sika Automotive AG</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Sheet</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Quelle</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Feld</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>N Zeilen</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Gefüllt%</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>Fehlt%</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>Bewertung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>✗ Lückenhaft</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>96</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>bi_raw</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Fracht</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Diesel</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Maut/SSD</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Dinas Gesamt</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>303</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger Land</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Empfänger PLZ</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Tonnage (eff.)</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Leistungsdatum</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>AX Fracht</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>AX Diesel</t>
+        </is>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>AX Maut</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>AX Nebengebühr</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>AX/BI</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>AX Gesamt</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>420</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>✓ OK</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
           <t>Daten-Qualität: Sika Automotive DE</t>
         </is>
       </c>
@@ -6801,7 +7697,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: GEZE GmbH</t>
+          <t>Daten-Qualität: Sika Supply Center GmbH</t>
         </is>
       </c>
     </row>
@@ -6859,17 +7755,17 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -6890,17 +7786,17 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -6921,17 +7817,17 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -6952,7 +7848,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -6983,17 +7879,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7014,17 +7910,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7045,17 +7941,17 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7076,17 +7972,17 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7107,17 +8003,17 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7138,17 +8034,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7169,17 +8065,17 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>149</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7200,17 +8096,17 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7231,17 +8127,17 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7262,17 +8158,17 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7293,17 +8189,17 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>99.3</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>0.7</v>
+        <v>100</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7324,17 +8220,17 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7355,17 +8251,17 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7386,17 +8282,17 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7417,17 +8313,17 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7448,17 +8344,17 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7479,17 +8375,17 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7510,17 +8406,17 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7541,17 +8437,17 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>7752</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -7584,7 +8480,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: HERMA GmbH</t>
+          <t>Daten-Qualität: GEZE GmbH</t>
         </is>
       </c>
     </row>
@@ -7642,17 +8538,17 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7673,17 +8569,17 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7704,17 +8600,17 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7735,7 +8631,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -7766,17 +8662,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7797,17 +8693,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7828,7 +8724,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -7859,7 +8755,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -7890,17 +8786,17 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7921,17 +8817,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>323</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
+        <v>149</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -7952,7 +8848,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>323</v>
+        <v>149</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -7983,17 +8879,17 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8014,17 +8910,17 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8045,17 +8941,17 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8076,17 +8972,17 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>99.3</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>100</v>
+        <v>0.7</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8107,17 +9003,17 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8138,17 +9034,17 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8169,17 +9065,17 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8200,7 +9096,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>5112</v>
+        <v>7752</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -8231,17 +9127,17 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8262,17 +9158,17 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8293,17 +9189,17 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>5112</v>
-      </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
+        <v>7752</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -8324,7 +9220,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>5112</v>
+        <v>7752</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -8367,7 +9263,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: Bitzer Kühlmaschinenbau</t>
+          <t>Daten-Qualität: HERMA GmbH</t>
         </is>
       </c>
     </row>
@@ -8425,17 +9321,17 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8456,17 +9352,17 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8487,17 +9383,17 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8518,7 +9414,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1596</v>
+        <v>323</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -8549,17 +9445,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>96.09999999999999</v>
+        <v>323</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3.9</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8580,17 +9476,17 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8611,7 +9507,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1596</v>
+        <v>323</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -8642,7 +9538,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1596</v>
+        <v>323</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -8673,17 +9569,17 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8704,17 +9600,17 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1596</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>100</v>
+        <v>323</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8735,7 +9631,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1596</v>
+        <v>323</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -8766,17 +9662,17 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8797,17 +9693,17 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8828,17 +9724,17 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8859,17 +9755,17 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>99</v>
+        <v>5112</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8890,17 +9786,17 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>99.90000000000001</v>
+        <v>5112</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0.1</v>
+        <v>100</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8921,17 +9817,17 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8952,17 +9848,17 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -8983,7 +9879,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>3474</v>
+        <v>5112</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -9014,17 +9910,17 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -9045,17 +9941,17 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -9076,17 +9972,17 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>3474</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>100</v>
+        <v>5112</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>✓ OK</t>
+          <t>✗ Lückenhaft</t>
         </is>
       </c>
     </row>
@@ -9107,7 +10003,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>3474</v>
+        <v>5112</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -9150,7 +10046,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: CHT Germany GmbH</t>
+          <t>Daten-Qualität: Bitzer Kühlmaschinenbau</t>
         </is>
       </c>
     </row>
@@ -9208,7 +10104,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>100</v>
@@ -9239,7 +10135,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>100</v>
@@ -9270,7 +10166,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>100</v>
@@ -9301,7 +10197,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -9332,13 +10228,13 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>100</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -9363,7 +10259,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>100</v>
@@ -9394,7 +10290,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -9425,7 +10321,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -9456,7 +10352,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -9487,7 +10383,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -9518,7 +10414,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>92</v>
+        <v>1596</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -9549,7 +10445,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -9580,7 +10476,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -9611,7 +10507,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -9642,13 +10538,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -9673,13 +10569,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -9704,7 +10600,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -9735,7 +10631,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -9766,7 +10662,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -9797,7 +10693,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -9828,7 +10724,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -9859,7 +10755,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -9890,7 +10786,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>779</v>
+        <v>3474</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -9933,7 +10829,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: Konrad Hornschuch GmbH</t>
+          <t>Daten-Qualität: CHT Germany GmbH</t>
         </is>
       </c>
     </row>
@@ -9991,7 +10887,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>100</v>
@@ -10022,7 +10918,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>100</v>
@@ -10053,7 +10949,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>100</v>
@@ -10084,7 +10980,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -10115,13 +11011,13 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -10146,7 +11042,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>100</v>
@@ -10177,7 +11073,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -10208,7 +11104,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -10239,7 +11135,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -10270,7 +11166,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -10301,7 +11197,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1365</v>
+        <v>92</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -10332,7 +11228,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -10363,7 +11259,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -10394,7 +11290,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -10425,13 +11321,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -10456,7 +11352,7 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>100</v>
@@ -10487,7 +11383,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -10518,7 +11414,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -10549,7 +11445,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -10580,7 +11476,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -10611,7 +11507,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -10642,7 +11538,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -10673,7 +11569,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2690</v>
+        <v>779</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>
@@ -10716,7 +11612,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Daten-Qualität: EBM-Papst Mulfingen</t>
+          <t>Daten-Qualität: Konrad Hornschuch GmbH</t>
         </is>
       </c>
     </row>
@@ -10774,7 +11670,7 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>100</v>
@@ -10805,7 +11701,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>100</v>
@@ -10836,7 +11732,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>100</v>
@@ -10867,7 +11763,7 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>0</v>
@@ -10898,17 +11794,17 @@
         </is>
       </c>
       <c r="D7" s="4" t="n">
-        <v>49</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>28.6</v>
+        <v>1365</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>97.40000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>71.40000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -10929,7 +11825,7 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>100</v>
@@ -10960,7 +11856,7 @@
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>100</v>
@@ -10991,7 +11887,7 @@
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>100</v>
@@ -11022,7 +11918,7 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>100</v>
@@ -11053,7 +11949,7 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>100</v>
@@ -11084,7 +11980,7 @@
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>49</v>
+        <v>1365</v>
       </c>
       <c r="E13" s="5" t="n">
         <v>100</v>
@@ -11115,7 +12011,7 @@
         </is>
       </c>
       <c r="D14" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E14" s="5" t="n">
         <v>100</v>
@@ -11146,7 +12042,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E15" s="5" t="n">
         <v>100</v>
@@ -11177,7 +12073,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>100</v>
@@ -11208,13 +12104,13 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>97.59999999999999</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="F17" s="8" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
@@ -11239,13 +12135,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
@@ -11270,7 +12166,7 @@
         </is>
       </c>
       <c r="D19" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>100</v>
@@ -11301,7 +12197,7 @@
         </is>
       </c>
       <c r="D20" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>100</v>
@@ -11332,7 +12228,7 @@
         </is>
       </c>
       <c r="D21" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>100</v>
@@ -11363,7 +12259,7 @@
         </is>
       </c>
       <c r="D22" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>100</v>
@@ -11394,7 +12290,7 @@
         </is>
       </c>
       <c r="D23" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>100</v>
@@ -11425,7 +12321,7 @@
         </is>
       </c>
       <c r="D24" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>100</v>
@@ -11456,7 +12352,7 @@
         </is>
       </c>
       <c r="D25" s="8" t="n">
-        <v>379</v>
+        <v>2690</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>100</v>

--- a/output/billing_report/00_audit_extraktion.xlsx
+++ b/output/billing_report/00_audit_extraktion.xlsx
@@ -1091,13 +1091,13 @@
         <v>113</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>543</v>
+        <v>792</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="G6" s="8" t="n">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="H6" s="8" t="n">
         <v>149</v>
@@ -1203,7 +1203,7 @@
         <v>333</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>442</v>
+        <v>3298</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>275</v>
@@ -1227,20 +1227,20 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="L7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
+      <c r="L7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="P7" s="6" t="n">
-        <v>0</v>
+      <c r="P7" s="5" t="n">
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7" s="6" t="n">
         <v>0</v>
@@ -1251,29 +1251,29 @@
       <c r="S7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="T7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="6" t="n">
-        <v>0</v>
+      <c r="T7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="U7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="V7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="W7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="6" t="n">
-        <v>0</v>
+      <c r="W7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="X7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="Y7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="Z7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" s="6" t="n">
-        <v>0</v>
+      <c r="AA7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="AB7" s="6" t="n">
         <v>0</v>
@@ -1284,14 +1284,14 @@
       <c r="AD7" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="AE7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="6" t="n">
-        <v>0</v>
+      <c r="AE7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF7" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="AG7" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="AH7" s="5" t="n">
         <v>100</v>
@@ -1315,7 +1315,7 @@
         <v>2004</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>4541</v>
+        <v>4819</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>4214</v>
@@ -1427,13 +1427,13 @@
         <v>191</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>144</v>
+        <v>255</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="H9" s="4" t="n">
         <v>92</v>
@@ -1539,7 +1539,7 @@
         <v>155</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>382</v>
+        <v>3382</v>
       </c>
       <c r="F10" s="8" t="n">
         <v>152</v>
@@ -1651,7 +1651,7 @@
         <v>178</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>123</v>
+        <v>613</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>118</v>
@@ -1763,13 +1763,13 @@
         <v>383</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>1347</v>
+        <v>5319</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>718</v>
+        <v>947</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>782</v>
+        <v>553</v>
       </c>
       <c r="H12" s="8" t="n">
         <v>526</v>
@@ -1903,14 +1903,14 @@
       <c r="M13" s="5" t="n">
         <v>98.90000000000001</v>
       </c>
-      <c r="N13" s="4" t="n">
-        <v>76.7</v>
+      <c r="N13" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="O13" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>1</v>
+        <v>15.7</v>
       </c>
       <c r="Q13" s="6" t="n">
         <v>0</v>
@@ -3904,15 +3904,15 @@
       <c r="D5" s="4" t="n">
         <v>1854</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>76.7</v>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>⚠ Teilweise</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -3967,10 +3967,10 @@
         <v>1854</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>15.7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>99</v>
+        <v>84.3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
@@ -9323,15 +9323,15 @@
       <c r="D3" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E3" s="6" t="n">
-        <v>0</v>
+      <c r="E3" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9354,15 +9354,15 @@
       <c r="D4" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E4" s="6" t="n">
-        <v>0</v>
+      <c r="E4" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9385,15 +9385,15 @@
       <c r="D5" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>0</v>
+      <c r="E5" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9447,15 +9447,15 @@
       <c r="D7" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>0</v>
+      <c r="E7" s="5" t="n">
+        <v>96.90000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>100</v>
+        <v>3.1</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9571,15 +9571,15 @@
       <c r="D11" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
+      <c r="E11" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9602,15 +9602,15 @@
       <c r="D12" s="4" t="n">
         <v>323</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>0</v>
+      <c r="E12" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9664,15 +9664,15 @@
       <c r="D14" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E14" s="6" t="n">
-        <v>0</v>
+      <c r="E14" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9695,15 +9695,15 @@
       <c r="D15" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E15" s="6" t="n">
-        <v>0</v>
+      <c r="E15" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9726,15 +9726,15 @@
       <c r="D16" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E16" s="6" t="n">
-        <v>0</v>
+      <c r="E16" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9788,15 +9788,15 @@
       <c r="D18" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E18" s="6" t="n">
-        <v>0</v>
+      <c r="E18" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9912,15 +9912,15 @@
       <c r="D22" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E22" s="6" t="n">
-        <v>0</v>
+      <c r="E22" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F22" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9943,15 +9943,15 @@
       <c r="D23" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E23" s="6" t="n">
-        <v>0</v>
+      <c r="E23" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F23" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
@@ -9974,15 +9974,15 @@
       <c r="D24" s="8" t="n">
         <v>5112</v>
       </c>
-      <c r="E24" s="6" t="n">
-        <v>0</v>
+      <c r="E24" s="5" t="n">
+        <v>100</v>
       </c>
       <c r="F24" s="8" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>✗ Lückenhaft</t>
+          <t>✓ OK</t>
         </is>
       </c>
     </row>
